--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,45 +1025,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137093758</v>
+        <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>96574</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674988</v>
+        <v>674840</v>
       </c>
       <c r="R5" t="n">
-        <v>6633802</v>
+        <v>6633851</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,62 +1120,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093758</t>
+          <t>https://artportalen.se/Sighting/137123332</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137093777</v>
+        <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92514</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>675022</v>
       </c>
       <c r="R6" t="n">
-        <v>6634173</v>
+        <v>6634179</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1232,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093777</t>
+          <t>https://artportalen.se/Sighting/137123336</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137093780</v>
+        <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>92514</v>
+        <v>96574</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675070</v>
+        <v>674988</v>
       </c>
       <c r="R7" t="n">
-        <v>6634182</v>
+        <v>6633802</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,16 +1355,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093780</t>
+          <t>https://artportalen.se/Sighting/137093758</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137093779</v>
+        <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>96574</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,37 +1372,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675044</v>
+        <v>674987</v>
       </c>
       <c r="R8" t="n">
-        <v>6634189</v>
+        <v>6633793</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,27 +1456,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093779</t>
+          <t>https://artportalen.se/Sighting/137123330</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137093759</v>
+        <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>58164</v>
+        <v>92514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103023</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674933</v>
+        <v>675022</v>
       </c>
       <c r="R9" t="n">
-        <v>6633792</v>
+        <v>6634173</v>
       </c>
       <c r="S9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,12 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1579,460 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137093777</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137093780</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92514</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>675070</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634182</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093780</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137093779</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>675044</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6634189</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093779</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137093759</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>674933</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6633792</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137093759</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137123331</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>674920</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633790</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123331</t>
         </is>
       </c>
     </row>
@@ -1598,6 +2046,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91648</v>
+        <v>91654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91654</v>
+        <v>91658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91660</v>
+        <v>91673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093759</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137123331</v>
       </c>
       <c r="B13" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91673</v>
+        <v>91675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093759</v>
       </c>
       <c r="B12" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137123331</v>
       </c>
       <c r="B13" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91675</v>
+        <v>91678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91678</v>
+        <v>91688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093759</v>
       </c>
       <c r="B12" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137123331</v>
       </c>
       <c r="B13" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093759</v>
       </c>
       <c r="B12" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137123331</v>
       </c>
       <c r="B13" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91692</v>
+        <v>91694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91694</v>
+        <v>91699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137093759</v>
       </c>
       <c r="B12" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137123331</v>
       </c>
       <c r="B13" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91699</v>
+        <v>91711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91711</v>
+        <v>91712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137093758</v>
       </c>
       <c r="B7" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137123330</v>
       </c>
       <c r="B8" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137093777</v>
       </c>
       <c r="B9" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137093780</v>
       </c>
       <c r="B10" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137093779</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,45 +1249,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137093758</v>
+        <v>137478632</v>
       </c>
       <c r="B7" t="n">
-        <v>96643</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>674988</v>
+        <v>674843</v>
       </c>
       <c r="R7" t="n">
-        <v>6633802</v>
+        <v>6633842</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,22 +1314,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,27 +1349,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093758</t>
+          <t>https://artportalen.se/Sighting/137478632</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137123330</v>
+        <v>137478635</v>
       </c>
       <c r="B8" t="n">
-        <v>96643</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2812</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>674987</v>
+        <v>674867</v>
       </c>
       <c r="R8" t="n">
-        <v>6633793</v>
+        <v>6633787</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,22 +1431,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,27 +1466,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137123330</t>
+          <t>https://artportalen.se/Sighting/137478635</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137093777</v>
+        <v>137478627</v>
       </c>
       <c r="B9" t="n">
-        <v>92578</v>
+        <v>96737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,34 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675022</v>
+        <v>674906</v>
       </c>
       <c r="R9" t="n">
-        <v>6634173</v>
+        <v>6633950</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,22 +1548,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på stenblock</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,27 +1583,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093777</t>
+          <t>https://artportalen.se/Sighting/137478627</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137093780</v>
+        <v>137093758</v>
       </c>
       <c r="B10" t="n">
-        <v>92578</v>
+        <v>96646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,13 +1635,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675070</v>
+        <v>674988</v>
       </c>
       <c r="R10" t="n">
-        <v>6634182</v>
+        <v>6633802</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,16 +1706,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093780</t>
+          <t>https://artportalen.se/Sighting/137093758</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137093779</v>
+        <v>137123330</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>96646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,37 +1723,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675044</v>
+        <v>674987</v>
       </c>
       <c r="R11" t="n">
-        <v>6634189</v>
+        <v>6633793</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,27 +1807,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093779</t>
+          <t>https://artportalen.se/Sighting/137123330</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137093759</v>
+        <v>137093777</v>
       </c>
       <c r="B12" t="n">
-        <v>58191</v>
+        <v>92581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103023</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,13 +1859,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674933</v>
+        <v>675022</v>
       </c>
       <c r="R12" t="n">
-        <v>6633792</v>
+        <v>6634173</v>
       </c>
       <c r="S12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,12 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,16 +1930,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093759</t>
+          <t>https://artportalen.se/Sighting/137093777</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137123331</v>
+        <v>137093780</v>
       </c>
       <c r="B13" t="n">
-        <v>58191</v>
+        <v>92581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,37 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103023</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örsjön, Upl</t>
+          <t>Örsjön Knivsta kn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674920</v>
+        <v>675070</v>
       </c>
       <c r="R13" t="n">
-        <v>6633790</v>
+        <v>6634182</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1996,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,18 +2031,1168 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137093780</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137478626</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92581</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>675074</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6634177</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478626</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137093779</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>675044</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634189</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093779</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137478631</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>674843</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6633851</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478631</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137478637</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>674883</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6633804</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478637</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137478633</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>674853</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6633832</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478633</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137478630</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>674875</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6633887</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning nedanför tall med blindtarmstömning</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478630</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137093759</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>674933</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6633792</v>
+      </c>
+      <c r="S20" t="n">
+        <v>19</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093759</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137123331</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>674920</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6633790</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137123331</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137478629</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>674892</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6633923</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På stående död björk</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478629</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137478634</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92576</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>674857</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6633828</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478634</t>
         </is>
       </c>
     </row>
@@ -2050,6 +3210,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,32 +1366,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137478635</v>
+        <v>137484366</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>674867</v>
+        <v>674844</v>
       </c>
       <c r="R8" t="n">
-        <v>6633787</v>
+        <v>6633848</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,49 +1466,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478635</t>
+          <t>https://artportalen.se/Sighting/137484366</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137478627</v>
+        <v>137484370</v>
       </c>
       <c r="B9" t="n">
-        <v>96737</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674906</v>
+        <v>674875</v>
       </c>
       <c r="R9" t="n">
-        <v>6633950</v>
+        <v>6633785</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växer på stenblock</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,27 +1578,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478627</t>
+          <t>https://artportalen.se/Sighting/137484370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137093758</v>
+        <v>137478635</v>
       </c>
       <c r="B10" t="n">
-        <v>96646</v>
+        <v>92859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,34 +1606,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2812</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674988</v>
+        <v>674867</v>
       </c>
       <c r="R10" t="n">
-        <v>6633802</v>
+        <v>6633787</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1665,22 +1660,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,27 +1695,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093758</t>
+          <t>https://artportalen.se/Sighting/137478635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137123330</v>
+        <v>137484369</v>
       </c>
       <c r="B11" t="n">
-        <v>96646</v>
+        <v>92859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2812</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674987</v>
+        <v>674871</v>
       </c>
       <c r="R11" t="n">
-        <v>6633793</v>
+        <v>6633785</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,22 +1777,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,16 +1818,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137123330</t>
+          <t>https://artportalen.se/Sighting/137484369</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137093777</v>
+        <v>137484360</v>
       </c>
       <c r="B12" t="n">
-        <v>92581</v>
+        <v>96752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,34 +1835,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>2668</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675022</v>
+        <v>674903</v>
       </c>
       <c r="R12" t="n">
-        <v>6634173</v>
+        <v>6633946</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1889,22 +1889,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,27 +1919,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093777</t>
+          <t>https://artportalen.se/Sighting/137484360</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137093780</v>
+        <v>137478627</v>
       </c>
       <c r="B13" t="n">
-        <v>92581</v>
+        <v>96737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,37 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675070</v>
+        <v>674906</v>
       </c>
       <c r="R13" t="n">
-        <v>6634182</v>
+        <v>6633950</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,22 +2001,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer på stenblock</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,27 +2036,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093780</t>
+          <t>https://artportalen.se/Sighting/137478627</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137478626</v>
+        <v>137484359</v>
       </c>
       <c r="B14" t="n">
-        <v>92581</v>
+        <v>96737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,21 +2064,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675074</v>
+        <v>674897</v>
       </c>
       <c r="R14" t="n">
-        <v>6634177</v>
+        <v>6633941</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,12 +2133,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på tall</t>
+          <t>På flyttblock</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,27 +2153,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478626</t>
+          <t>https://artportalen.se/Sighting/137484359</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137093779</v>
+        <v>137093758</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>96646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2200,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675044</v>
+        <v>674988</v>
       </c>
       <c r="R15" t="n">
-        <v>6634189</v>
+        <v>6633802</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2235,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,16 +2276,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093779</t>
+          <t>https://artportalen.se/Sighting/137093758</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137478631</v>
+        <v>137123330</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>96646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,21 +2293,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2312,13 +2317,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674843</v>
+        <v>674987</v>
       </c>
       <c r="R16" t="n">
-        <v>6633851</v>
+        <v>6633793</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,27 +2347,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,27 +2377,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478631</t>
+          <t>https://artportalen.se/Sighting/137123330</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137478637</v>
+        <v>137484363</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>96646</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674883</v>
+        <v>674881</v>
       </c>
       <c r="R17" t="n">
-        <v>6633804</v>
+        <v>6633895</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,62 +2489,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478637</t>
+          <t>https://artportalen.se/Sighting/137484363</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137478633</v>
+        <v>137093777</v>
       </c>
       <c r="B18" t="n">
-        <v>93523</v>
+        <v>92581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örsjön, Upl</t>
+          <t>Örsjön Knivsta kn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674853</v>
+        <v>675022</v>
       </c>
       <c r="R18" t="n">
-        <v>6633832</v>
+        <v>6634173</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,27 +2601,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478633</t>
+          <t>https://artportalen.se/Sighting/137093777</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137478630</v>
+        <v>137093780</v>
       </c>
       <c r="B19" t="n">
-        <v>57221</v>
+        <v>92581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,37 +2629,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örsjön, Upl</t>
+          <t>Örsjön Knivsta kn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674875</v>
+        <v>675070</v>
       </c>
       <c r="R19" t="n">
-        <v>6633887</v>
+        <v>6634182</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2683,27 +2683,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spillning nedanför tall med blindtarmstömning</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,27 +2713,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Karin Lieber</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478630</t>
+          <t>https://artportalen.se/Sighting/137093780</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137093759</v>
+        <v>137478626</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
+        <v>92581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,37 +2741,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>4217</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örsjön Knivsta kn, Upl</t>
+          <t>Örsjön, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674933</v>
+        <v>675074</v>
       </c>
       <c r="R20" t="n">
-        <v>6633792</v>
+        <v>6634177</v>
       </c>
       <c r="S20" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2800,27 +2795,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>Växer på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,27 +2830,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anna-Karin Lieber</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093759</t>
+          <t>https://artportalen.se/Sighting/137478626</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137123331</v>
+        <v>137093779</v>
       </c>
       <c r="B21" t="n">
-        <v>58191</v>
+        <v>92148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,37 +2858,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103023</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Örsjön, Upl</t>
+          <t>Örsjön Knivsta kn, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674920</v>
+        <v>675044</v>
       </c>
       <c r="R21" t="n">
-        <v>6633790</v>
+        <v>6634189</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,7 +2917,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2927,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,27 +2942,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ylva Petersson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137123331</t>
+          <t>https://artportalen.se/Sighting/137093779</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137478629</v>
+        <v>137478631</v>
       </c>
       <c r="B22" t="n">
-        <v>8459</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,21 +2970,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674892</v>
+        <v>674843</v>
       </c>
       <c r="R22" t="n">
-        <v>6633923</v>
+        <v>6633851</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3034,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,12 +3039,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På stående död björk</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,38 +3070,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137478629</t>
+          <t>https://artportalen.se/Sighting/137478631</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137478634</v>
+        <v>137478637</v>
       </c>
       <c r="B23" t="n">
-        <v>92576</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3116,13 +3111,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674857</v>
+        <v>674883</v>
       </c>
       <c r="R23" t="n">
-        <v>6633828</v>
+        <v>6633804</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3151,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,12 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,7 +3182,1396 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137478637</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137484357</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>675036</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634187</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Granlega</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484357</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137484365</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>674841</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6633849</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484365</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137478633</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>674853</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6633832</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478633</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137484367</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>674852</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6633830</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484367</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137478630</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>674875</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6633887</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillning nedanför tall med blindtarmstömning</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478630</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137484364</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>674868</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6633889</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spillning under tall, flera blindtarmstömningar</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484364</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137093759</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Örsjön Knivsta kn, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>674933</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6633792</v>
+      </c>
+      <c r="S30" t="n">
+        <v>19</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137093759</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137123331</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>674920</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6633790</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123331</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137478629</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>674892</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6633923</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På stående död björk</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137478629</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137484362</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>674892</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6633941</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Stående död björk</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484362</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137478634</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92576</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>674857</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6633828</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Karin Lieber</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137478634</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137484368</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92576</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>674862</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6633843</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137484368</t>
         </is>
       </c>
     </row>
@@ -3220,6 +4599,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35395-2026 artfynd.xlsx
+++ b/artfynd/A 35395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093782</v>
       </c>
       <c r="B2" t="n">
-        <v>91715</v>
+        <v>91719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137093776</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137093778</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137123332</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137123336</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137478632</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137484366</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137484370</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137478635</v>
       </c>
       <c r="B10" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137484369</v>
       </c>
       <c r="B11" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>137484360</v>
       </c>
       <c r="B12" t="n">
-        <v>96752</v>
+        <v>96756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137478627</v>
       </c>
       <c r="B13" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>137484359</v>
       </c>
       <c r="B14" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137093758</v>
       </c>
       <c r="B15" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>137123330</v>
       </c>
       <c r="B16" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137484363</v>
       </c>
       <c r="B17" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>137093777</v>
       </c>
       <c r="B18" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137093780</v>
       </c>
       <c r="B19" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>137478626</v>
       </c>
       <c r="B20" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>137093779</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>137478631</v>
       </c>
       <c r="B22" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>137478637</v>
       </c>
       <c r="B23" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>137484357</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>137484365</v>
       </c>
       <c r="B25" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>137478633</v>
       </c>
       <c r="B26" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>137484367</v>
       </c>
       <c r="B27" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>137478630</v>
       </c>
       <c r="B28" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>137484364</v>
       </c>
       <c r="B29" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>137093759</v>
       </c>
       <c r="B30" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137123331</v>
       </c>
       <c r="B31" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>137478634</v>
       </c>
       <c r="B34" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>137484368</v>
       </c>
       <c r="B35" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
